--- a/converted_files/837/837I-all-fields.xlsx
+++ b/converted_files/837/837I-all-fields.xlsx
@@ -59,7 +59,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:MW3"/>
+  <dimension ref="A1:MZ3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1020,850 +1020,865 @@
       </c>
       <c r="GJ1" s="3" t="inlineStr">
         <is>
+          <t>Treatment1Code</t>
+        </is>
+      </c>
+      <c r="GK1" s="3" t="inlineStr">
+        <is>
+          <t>Treatment2Code</t>
+        </is>
+      </c>
+      <c r="GL1" s="3" t="inlineStr">
+        <is>
+          <t>Treatment3Code</t>
+        </is>
+      </c>
+      <c r="GM1" s="3" t="inlineStr">
+        <is>
           <t>Attachment1ReportTypeCode</t>
         </is>
       </c>
-      <c r="GK1" s="3" t="inlineStr">
+      <c r="GN1" s="3" t="inlineStr">
         <is>
           <t>Attachment1ReportTransmissionCode</t>
         </is>
       </c>
-      <c r="GL1" s="3" t="inlineStr">
+      <c r="GO1" s="3" t="inlineStr">
         <is>
           <t>Attachment1ControlNumber</t>
         </is>
       </c>
-      <c r="GM1" s="3" t="inlineStr">
+      <c r="GP1" s="3" t="inlineStr">
         <is>
           <t>Attachment2ReportTypeCode</t>
         </is>
       </c>
-      <c r="GN1" s="3" t="inlineStr">
+      <c r="GQ1" s="3" t="inlineStr">
         <is>
           <t>Attachment2ReportTransmissionCode</t>
         </is>
       </c>
-      <c r="GO1" s="3" t="inlineStr">
+      <c r="GR1" s="3" t="inlineStr">
         <is>
           <t>Attachment2ControlNumber</t>
         </is>
       </c>
-      <c r="GP1" s="3" t="inlineStr">
+      <c r="GS1" s="3" t="inlineStr">
         <is>
           <t>Attachment3ReportTypeCode</t>
         </is>
       </c>
-      <c r="GQ1" s="3" t="inlineStr">
+      <c r="GT1" s="3" t="inlineStr">
         <is>
           <t>Attachment3ReportTransmissionCode</t>
         </is>
       </c>
-      <c r="GR1" s="3" t="inlineStr">
+      <c r="GU1" s="3" t="inlineStr">
         <is>
           <t>Attachment3ControlNumber</t>
         </is>
       </c>
-      <c r="GS1" s="3" t="inlineStr">
+      <c r="GV1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderIdentifier</t>
         </is>
       </c>
-      <c r="GT1" s="3" t="inlineStr">
+      <c r="GW1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="GU1" s="3" t="inlineStr">
+      <c r="GX1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderFirstName</t>
         </is>
       </c>
-      <c r="GV1" s="3" t="inlineStr">
+      <c r="GY1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderMiddleName</t>
         </is>
       </c>
-      <c r="GW1" s="3" t="inlineStr">
+      <c r="GZ1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderProviderTaxonomyCode</t>
         </is>
       </c>
-      <c r="GX1" s="3" t="inlineStr">
+      <c r="HA1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderAdditionalId1Type</t>
         </is>
       </c>
-      <c r="GY1" s="3" t="inlineStr">
+      <c r="HB1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="GZ1" s="3" t="inlineStr">
+      <c r="HC1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderAdditionalId2Type</t>
         </is>
       </c>
-      <c r="HA1" s="3" t="inlineStr">
+      <c r="HD1" s="3" t="inlineStr">
         <is>
           <t>AttendingProviderAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="HB1" s="3" t="inlineStr">
+      <c r="HE1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianIdentifier</t>
         </is>
       </c>
-      <c r="HC1" s="3" t="inlineStr">
+      <c r="HF1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="HD1" s="3" t="inlineStr">
+      <c r="HG1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianFirstName</t>
         </is>
       </c>
-      <c r="HE1" s="3" t="inlineStr">
+      <c r="HH1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianMiddleName</t>
         </is>
       </c>
-      <c r="HF1" s="3" t="inlineStr">
+      <c r="HI1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianAdditionalId1Type</t>
         </is>
       </c>
-      <c r="HG1" s="3" t="inlineStr">
+      <c r="HJ1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="HH1" s="3" t="inlineStr">
+      <c r="HK1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianAdditionalId2Type</t>
         </is>
       </c>
-      <c r="HI1" s="3" t="inlineStr">
+      <c r="HL1" s="3" t="inlineStr">
         <is>
           <t>OperatingPhysicianAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="HJ1" s="3" t="inlineStr">
+      <c r="HM1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianIdentifier</t>
         </is>
       </c>
-      <c r="HK1" s="3" t="inlineStr">
+      <c r="HN1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="HL1" s="3" t="inlineStr">
+      <c r="HO1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianFirstName</t>
         </is>
       </c>
-      <c r="HM1" s="3" t="inlineStr">
+      <c r="HP1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianMiddleName</t>
         </is>
       </c>
-      <c r="HN1" s="3" t="inlineStr">
+      <c r="HQ1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianAdditionalId1Type</t>
         </is>
       </c>
-      <c r="HO1" s="3" t="inlineStr">
+      <c r="HR1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="HP1" s="3" t="inlineStr">
+      <c r="HS1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianAdditionalId2Type</t>
         </is>
       </c>
-      <c r="HQ1" s="3" t="inlineStr">
+      <c r="HT1" s="3" t="inlineStr">
         <is>
           <t>OtherOperatingPhysicianAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="HR1" s="3" t="inlineStr">
+      <c r="HU1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderIdentifier</t>
         </is>
       </c>
-      <c r="HS1" s="3" t="inlineStr">
+      <c r="HV1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="HT1" s="3" t="inlineStr">
+      <c r="HW1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderFirstName</t>
         </is>
       </c>
-      <c r="HU1" s="3" t="inlineStr">
+      <c r="HX1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderMiddleName</t>
         </is>
       </c>
-      <c r="HV1" s="3" t="inlineStr">
+      <c r="HY1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderAdditionalId1Type</t>
         </is>
       </c>
-      <c r="HW1" s="3" t="inlineStr">
+      <c r="HZ1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="HX1" s="3" t="inlineStr">
+      <c r="IA1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderAdditionalId2Type</t>
         </is>
       </c>
-      <c r="HY1" s="3" t="inlineStr">
+      <c r="IB1" s="3" t="inlineStr">
         <is>
           <t>ReferringProviderAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="HZ1" s="3" t="inlineStr">
+      <c r="IC1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderIdentifier</t>
         </is>
       </c>
-      <c r="IA1" s="3" t="inlineStr">
+      <c r="ID1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="IB1" s="3" t="inlineStr">
+      <c r="IE1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderFirstName</t>
         </is>
       </c>
-      <c r="IC1" s="3" t="inlineStr">
+      <c r="IF1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderMiddleName</t>
         </is>
       </c>
-      <c r="ID1" s="3" t="inlineStr">
+      <c r="IG1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderAdditionalId1Type</t>
         </is>
       </c>
-      <c r="IE1" s="3" t="inlineStr">
+      <c r="IH1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="IF1" s="3" t="inlineStr">
+      <c r="II1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderAdditionalId2Type</t>
         </is>
       </c>
-      <c r="IG1" s="3" t="inlineStr">
+      <c r="IJ1" s="3" t="inlineStr">
         <is>
           <t>RenderingProviderAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="IH1" s="3" t="inlineStr">
+      <c r="IK1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityIdentifier</t>
         </is>
       </c>
-      <c r="II1" s="3" t="inlineStr">
+      <c r="IL1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityName</t>
         </is>
       </c>
-      <c r="IJ1" s="3" t="inlineStr">
+      <c r="IM1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAddressLine</t>
         </is>
       </c>
-      <c r="IK1" s="3" t="inlineStr">
+      <c r="IN1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAddressLine2</t>
         </is>
       </c>
-      <c r="IL1" s="3" t="inlineStr">
+      <c r="IO1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAddressCity</t>
         </is>
       </c>
-      <c r="IM1" s="3" t="inlineStr">
+      <c r="IP1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAddressStateCode</t>
         </is>
       </c>
-      <c r="IN1" s="3" t="inlineStr">
+      <c r="IQ1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAddressZipCode</t>
         </is>
       </c>
-      <c r="IO1" s="3" t="inlineStr">
+      <c r="IR1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAdditionalId1Type</t>
         </is>
       </c>
-      <c r="IP1" s="3" t="inlineStr">
+      <c r="IS1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="IQ1" s="3" t="inlineStr">
+      <c r="IT1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAdditionalId2Type</t>
         </is>
       </c>
-      <c r="IR1" s="3" t="inlineStr">
+      <c r="IU1" s="3" t="inlineStr">
         <is>
           <t>ServiceFacilityAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="IS1" s="3" t="inlineStr">
+      <c r="IV1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerResponsibilitySequence</t>
         </is>
       </c>
-      <c r="IT1" s="3" t="inlineStr">
+      <c r="IW1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberRelationshipType</t>
         </is>
       </c>
-      <c r="IU1" s="3" t="inlineStr">
+      <c r="IX1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberGroupOrPolicyNumber</t>
         </is>
       </c>
-      <c r="IV1" s="3" t="inlineStr">
+      <c r="IY1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberGroupName</t>
         </is>
       </c>
-      <c r="IW1" s="3" t="inlineStr">
+      <c r="IZ1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberClaimFilingIndicatorCode</t>
         </is>
       </c>
-      <c r="IX1" s="3" t="inlineStr">
+      <c r="JA1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberIdentificationType</t>
         </is>
       </c>
-      <c r="IY1" s="3" t="inlineStr">
+      <c r="JB1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberIdentifier</t>
         </is>
       </c>
-      <c r="IZ1" s="3" t="inlineStr">
+      <c r="JC1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberTaxId</t>
         </is>
       </c>
-      <c r="JA1" s="3" t="inlineStr">
+      <c r="JD1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberLastName</t>
         </is>
       </c>
-      <c r="JB1" s="3" t="inlineStr">
+      <c r="JE1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberFirstName</t>
         </is>
       </c>
-      <c r="JC1" s="3" t="inlineStr">
+      <c r="JF1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberMiddleName</t>
         </is>
       </c>
-      <c r="JD1" s="3" t="inlineStr">
+      <c r="JG1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAddressLine</t>
         </is>
       </c>
-      <c r="JE1" s="3" t="inlineStr">
+      <c r="JH1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAddressLine2</t>
         </is>
       </c>
-      <c r="JF1" s="3" t="inlineStr">
+      <c r="JI1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAddressCity</t>
         </is>
       </c>
-      <c r="JG1" s="3" t="inlineStr">
+      <c r="JJ1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAddressStateCode</t>
         </is>
       </c>
-      <c r="JH1" s="3" t="inlineStr">
+      <c r="JK1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAddressZipCode</t>
         </is>
       </c>
-      <c r="JI1" s="3" t="inlineStr">
+      <c r="JL1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment1Group</t>
         </is>
       </c>
-      <c r="JJ1" s="3" t="inlineStr">
+      <c r="JM1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment1ReasonCode</t>
         </is>
       </c>
-      <c r="JK1" s="3" t="inlineStr">
+      <c r="JN1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment1Amount</t>
         </is>
       </c>
-      <c r="JL1" s="3" t="inlineStr">
+      <c r="JO1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment1Quantity</t>
         </is>
       </c>
-      <c r="JM1" s="3" t="inlineStr">
+      <c r="JP1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment2Group</t>
         </is>
       </c>
-      <c r="JN1" s="3" t="inlineStr">
+      <c r="JQ1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment2ReasonCode</t>
         </is>
       </c>
-      <c r="JO1" s="3" t="inlineStr">
+      <c r="JR1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment2Amount</t>
         </is>
       </c>
-      <c r="JP1" s="3" t="inlineStr">
+      <c r="JS1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment2Quantity</t>
         </is>
       </c>
-      <c r="JQ1" s="3" t="inlineStr">
+      <c r="JT1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment3Group</t>
         </is>
       </c>
-      <c r="JR1" s="3" t="inlineStr">
+      <c r="JU1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment3ReasonCode</t>
         </is>
       </c>
-      <c r="JS1" s="3" t="inlineStr">
+      <c r="JV1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment3Amount</t>
         </is>
       </c>
-      <c r="JT1" s="3" t="inlineStr">
+      <c r="JW1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberAdjustment3Quantity</t>
         </is>
       </c>
-      <c r="JU1" s="3" t="inlineStr">
+      <c r="JX1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerPaidAmount</t>
         </is>
       </c>
-      <c r="JV1" s="3" t="inlineStr">
+      <c r="JY1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberNonCoveredAmount</t>
         </is>
       </c>
-      <c r="JW1" s="3" t="inlineStr">
+      <c r="JZ1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberRemainingPatientLiabilityAmount</t>
         </is>
       </c>
-      <c r="JX1" s="3" t="inlineStr">
+      <c r="KA1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerClaimControlNumber</t>
         </is>
       </c>
-      <c r="JY1" s="3" t="inlineStr">
+      <c r="KB1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerIdentificationType</t>
         </is>
       </c>
-      <c r="JZ1" s="3" t="inlineStr">
+      <c r="KC1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerIdentifier</t>
         </is>
       </c>
-      <c r="KA1" s="3" t="inlineStr">
+      <c r="KD1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerTaxId</t>
         </is>
       </c>
-      <c r="KB1" s="3" t="inlineStr">
+      <c r="KE1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerName</t>
         </is>
       </c>
-      <c r="KC1" s="3" t="inlineStr">
+      <c r="KF1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAddressLine</t>
         </is>
       </c>
-      <c r="KD1" s="3" t="inlineStr">
+      <c r="KG1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAddressLine2</t>
         </is>
       </c>
-      <c r="KE1" s="3" t="inlineStr">
+      <c r="KH1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAddressCity</t>
         </is>
       </c>
-      <c r="KF1" s="3" t="inlineStr">
+      <c r="KI1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAddressStateCode</t>
         </is>
       </c>
-      <c r="KG1" s="3" t="inlineStr">
+      <c r="KJ1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAddressZipCode</t>
         </is>
       </c>
-      <c r="KH1" s="3" t="inlineStr">
+      <c r="KK1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAdditionalId1Type</t>
         </is>
       </c>
-      <c r="KI1" s="3" t="inlineStr">
+      <c r="KL1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="KJ1" s="3" t="inlineStr">
+      <c r="KM1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAdditionalId2Type</t>
         </is>
       </c>
-      <c r="KK1" s="3" t="inlineStr">
+      <c r="KN1" s="3" t="inlineStr">
         <is>
           <t>OtherSubscriberPayerAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="KL1" s="3" t="inlineStr">
+      <c r="KO1" s="3" t="inlineStr">
         <is>
           <t>LineControlNumber</t>
         </is>
       </c>
-      <c r="KM1" s="3" t="inlineStr">
+      <c r="KP1" s="3" t="inlineStr">
         <is>
           <t>LineRevenueCodeCode</t>
         </is>
       </c>
-      <c r="KN1" s="3" t="inlineStr">
+      <c r="KQ1" s="3" t="inlineStr">
         <is>
           <t>LineProcedureCode</t>
         </is>
       </c>
-      <c r="KO1" s="3" t="inlineStr">
+      <c r="KR1" s="3" t="inlineStr">
         <is>
           <t>LineProcedureDescFromClaim</t>
         </is>
       </c>
-      <c r="KP1" s="3" t="inlineStr">
+      <c r="KS1" s="3" t="inlineStr">
         <is>
           <t>LineProcedureModifier1Code</t>
         </is>
       </c>
-      <c r="KQ1" s="3" t="inlineStr">
+      <c r="KT1" s="3" t="inlineStr">
         <is>
           <t>LineProcedureModifier2Code</t>
         </is>
       </c>
-      <c r="KR1" s="3" t="inlineStr">
+      <c r="KU1" s="3" t="inlineStr">
         <is>
           <t>LineProcedureModifier3Code</t>
         </is>
       </c>
-      <c r="KS1" s="3" t="inlineStr">
+      <c r="KV1" s="3" t="inlineStr">
         <is>
           <t>LineProcedureModifier4Code</t>
         </is>
       </c>
-      <c r="KT1" s="3" t="inlineStr">
+      <c r="KW1" s="3" t="inlineStr">
         <is>
           <t>LineChargeAmount</t>
         </is>
       </c>
-      <c r="KU1" s="3" t="inlineStr">
+      <c r="KX1" s="3" t="inlineStr">
         <is>
           <t>LineUnitType</t>
         </is>
       </c>
-      <c r="KV1" s="3" t="inlineStr">
+      <c r="KY1" s="3" t="inlineStr">
         <is>
           <t>LineUnitCount</t>
         </is>
       </c>
-      <c r="KW1" s="3" t="inlineStr">
+      <c r="KZ1" s="3" t="inlineStr">
         <is>
           <t>LineNonCoveredAmount</t>
         </is>
       </c>
-      <c r="KX1" s="3" t="inlineStr">
+      <c r="LA1" s="3" t="inlineStr">
         <is>
           <t>LineServiceDateFrom</t>
         </is>
       </c>
-      <c r="KY1" s="3" t="inlineStr">
+      <c r="LB1" s="3" t="inlineStr">
         <is>
           <t>LineServiceDateTo</t>
         </is>
       </c>
-      <c r="KZ1" s="3" t="inlineStr">
+      <c r="LC1" s="3" t="inlineStr">
         <is>
           <t>LineRepricedReferenceNumber</t>
         </is>
       </c>
-      <c r="LA1" s="3" t="inlineStr">
+      <c r="LD1" s="3" t="inlineStr">
         <is>
           <t>LineAdjustedRepricedReferenceNumber</t>
         </is>
       </c>
-      <c r="LB1" s="3" t="inlineStr">
+      <c r="LE1" s="3" t="inlineStr">
         <is>
           <t>LineServiceTaxAmount</t>
         </is>
       </c>
-      <c r="LC1" s="3" t="inlineStr">
+      <c r="LF1" s="3" t="inlineStr">
         <is>
           <t>LineFacilityTaxAmount</t>
         </is>
       </c>
-      <c r="LD1" s="3" t="inlineStr">
+      <c r="LG1" s="3" t="inlineStr">
         <is>
           <t>LineThirdPartyNote</t>
         </is>
       </c>
-      <c r="LE1" s="3" t="inlineStr">
+      <c r="LH1" s="3" t="inlineStr">
         <is>
           <t>LineDrugCode</t>
         </is>
       </c>
-      <c r="LF1" s="3" t="inlineStr">
+      <c r="LI1" s="3" t="inlineStr">
         <is>
           <t>LineDrugQuantity</t>
         </is>
       </c>
-      <c r="LG1" s="3" t="inlineStr">
+      <c r="LJ1" s="3" t="inlineStr">
         <is>
           <t>LineDrugUnitType</t>
         </is>
       </c>
-      <c r="LH1" s="3" t="inlineStr">
+      <c r="LK1" s="3" t="inlineStr">
         <is>
           <t>LinePrescriptionNumber</t>
         </is>
       </c>
-      <c r="LI1" s="3" t="inlineStr">
+      <c r="LL1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment1ReportTypeCode</t>
         </is>
       </c>
-      <c r="LJ1" s="3" t="inlineStr">
+      <c r="LM1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment1ReportTransmissionCode</t>
         </is>
       </c>
-      <c r="LK1" s="3" t="inlineStr">
+      <c r="LN1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment1ControlNumber</t>
         </is>
       </c>
-      <c r="LL1" s="3" t="inlineStr">
+      <c r="LO1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment2ReportTypeCode</t>
         </is>
       </c>
-      <c r="LM1" s="3" t="inlineStr">
+      <c r="LP1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment2ReportTransmissionCode</t>
         </is>
       </c>
-      <c r="LN1" s="3" t="inlineStr">
+      <c r="LQ1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment2ControlNumber</t>
         </is>
       </c>
-      <c r="LO1" s="3" t="inlineStr">
+      <c r="LR1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment3ReportTypeCode</t>
         </is>
       </c>
-      <c r="LP1" s="3" t="inlineStr">
+      <c r="LS1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment3ReportTransmissionCode</t>
         </is>
       </c>
-      <c r="LQ1" s="3" t="inlineStr">
+      <c r="LT1" s="3" t="inlineStr">
         <is>
           <t>LineAttachment3ControlNumber</t>
         </is>
       </c>
-      <c r="LR1" s="3" t="inlineStr">
+      <c r="LU1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianIdentifier</t>
         </is>
       </c>
-      <c r="LS1" s="3" t="inlineStr">
+      <c r="LV1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="LT1" s="3" t="inlineStr">
+      <c r="LW1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianFirstName</t>
         </is>
       </c>
-      <c r="LU1" s="3" t="inlineStr">
+      <c r="LX1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianMiddleName</t>
         </is>
       </c>
-      <c r="LV1" s="3" t="inlineStr">
+      <c r="LY1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianAdditionalId1Type</t>
         </is>
       </c>
-      <c r="LW1" s="3" t="inlineStr">
+      <c r="LZ1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="LX1" s="3" t="inlineStr">
+      <c r="MA1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianAdditionalId2Type</t>
         </is>
       </c>
-      <c r="LY1" s="3" t="inlineStr">
+      <c r="MB1" s="3" t="inlineStr">
         <is>
           <t>LineOperatingPhysicianAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="LZ1" s="3" t="inlineStr">
+      <c r="MC1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianIdentifier</t>
         </is>
       </c>
-      <c r="MA1" s="3" t="inlineStr">
+      <c r="MD1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="MB1" s="3" t="inlineStr">
+      <c r="ME1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianFirstName</t>
         </is>
       </c>
-      <c r="MC1" s="3" t="inlineStr">
+      <c r="MF1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianMiddleName</t>
         </is>
       </c>
-      <c r="MD1" s="3" t="inlineStr">
+      <c r="MG1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianAdditionalId1Type</t>
         </is>
       </c>
-      <c r="ME1" s="3" t="inlineStr">
+      <c r="MH1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="MF1" s="3" t="inlineStr">
+      <c r="MI1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianAdditionalId2Type</t>
         </is>
       </c>
-      <c r="MG1" s="3" t="inlineStr">
+      <c r="MJ1" s="3" t="inlineStr">
         <is>
           <t>LineOtherOperatingPhysicianAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="MH1" s="3" t="inlineStr">
+      <c r="MK1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderIdentifier</t>
         </is>
       </c>
-      <c r="MI1" s="3" t="inlineStr">
+      <c r="ML1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="MJ1" s="3" t="inlineStr">
+      <c r="MM1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderFirstName</t>
         </is>
       </c>
-      <c r="MK1" s="3" t="inlineStr">
+      <c r="MN1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderMiddleName</t>
         </is>
       </c>
-      <c r="ML1" s="3" t="inlineStr">
+      <c r="MO1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderAdditionalId1Type</t>
         </is>
       </c>
-      <c r="MM1" s="3" t="inlineStr">
+      <c r="MP1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="MN1" s="3" t="inlineStr">
+      <c r="MQ1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderAdditionalId2Type</t>
         </is>
       </c>
-      <c r="MO1" s="3" t="inlineStr">
+      <c r="MR1" s="3" t="inlineStr">
         <is>
           <t>LineRenderingProviderAdditionalId2Identification</t>
         </is>
       </c>
-      <c r="MP1" s="3" t="inlineStr">
+      <c r="MS1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderIdentifier</t>
         </is>
       </c>
-      <c r="MQ1" s="3" t="inlineStr">
+      <c r="MT1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderLastNameOrOrgName</t>
         </is>
       </c>
-      <c r="MR1" s="3" t="inlineStr">
+      <c r="MU1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderFirstName</t>
         </is>
       </c>
-      <c r="MS1" s="3" t="inlineStr">
+      <c r="MV1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderMiddleName</t>
         </is>
       </c>
-      <c r="MT1" s="3" t="inlineStr">
+      <c r="MW1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderAdditionalId1Type</t>
         </is>
       </c>
-      <c r="MU1" s="3" t="inlineStr">
+      <c r="MX1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderAdditionalId1Identification</t>
         </is>
       </c>
-      <c r="MV1" s="3" t="inlineStr">
+      <c r="MY1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderAdditionalId2Type</t>
         </is>
       </c>
-      <c r="MW1" s="3" t="inlineStr">
+      <c r="MZ1" s="3" t="inlineStr">
         <is>
           <t>LineReferringProviderAdditionalId2Identification</t>
         </is>
@@ -1872,7 +1887,7 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6497613a0e49909442</t>
+          <t>6aaaca96b439338235b48e7d</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -2625,613 +2640,624 @@
       </c>
       <c r="GJ2" s="3" t="inlineStr">
         <is>
+          <t>A01</t>
+        </is>
+      </c>
+      <c r="GK2" s="3" t="inlineStr">
+        <is>
+          <t>A02</t>
+        </is>
+      </c>
+      <c r="GL2"/>
+      <c r="GM2" s="3" t="inlineStr">
+        <is>
           <t>OZ</t>
         </is>
       </c>
-      <c r="GK2" s="3" t="inlineStr">
+      <c r="GN2" s="3" t="inlineStr">
         <is>
           <t>BM</t>
         </is>
       </c>
-      <c r="GL2" s="3" t="inlineStr">
+      <c r="GO2" s="3" t="inlineStr">
         <is>
           <t>DMN0012</t>
         </is>
       </c>
-      <c r="GM2"/>
-      <c r="GN2"/>
-      <c r="GO2"/>
       <c r="GP2"/>
       <c r="GQ2"/>
       <c r="GR2"/>
-      <c r="GS2" s="3" t="inlineStr">
+      <c r="GS2"/>
+      <c r="GT2"/>
+      <c r="GU2"/>
+      <c r="GV2" s="3" t="inlineStr">
         <is>
           <t>1699222100</t>
         </is>
       </c>
-      <c r="GT2" s="3" t="inlineStr">
+      <c r="GW2" s="3" t="inlineStr">
         <is>
           <t>JONES</t>
         </is>
       </c>
-      <c r="GU2" s="3" t="inlineStr">
+      <c r="GX2" s="3" t="inlineStr">
         <is>
           <t>ALEX</t>
         </is>
       </c>
-      <c r="GV2" s="3" t="inlineStr">
+      <c r="GY2" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="GW2" s="3" t="inlineStr">
+      <c r="GZ2" s="3" t="inlineStr">
         <is>
           <t>208D00000X</t>
         </is>
       </c>
-      <c r="GX2" s="3" t="inlineStr">
+      <c r="HA2" s="3" t="inlineStr">
         <is>
           <t>LOCATION_NUMBER</t>
         </is>
       </c>
-      <c r="GY2" s="3" t="inlineStr">
+      <c r="HB2" s="3" t="inlineStr">
         <is>
           <t>12345</t>
         </is>
       </c>
-      <c r="GZ2"/>
-      <c r="HA2"/>
-      <c r="HB2" s="3" t="inlineStr">
+      <c r="HC2"/>
+      <c r="HD2"/>
+      <c r="HE2" s="3" t="inlineStr">
         <is>
           <t>OPRDOC1234</t>
         </is>
       </c>
-      <c r="HC2" s="3" t="inlineStr">
+      <c r="HF2" s="3" t="inlineStr">
         <is>
           <t>BELL</t>
         </is>
       </c>
-      <c r="HD2" s="3" t="inlineStr">
+      <c r="HG2" s="3" t="inlineStr">
         <is>
           <t>RITA</t>
         </is>
       </c>
-      <c r="HE2" s="3" t="inlineStr">
+      <c r="HH2" s="3" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="HF2"/>
-      <c r="HG2"/>
-      <c r="HH2"/>
       <c r="HI2"/>
-      <c r="HJ2" s="3" t="inlineStr">
+      <c r="HJ2"/>
+      <c r="HK2"/>
+      <c r="HL2"/>
+      <c r="HM2" s="3" t="inlineStr">
         <is>
           <t>OTHOPR1234</t>
         </is>
       </c>
-      <c r="HK2" s="3" t="inlineStr">
+      <c r="HN2" s="3" t="inlineStr">
         <is>
           <t>JOHNSON</t>
         </is>
       </c>
-      <c r="HL2" s="3" t="inlineStr">
+      <c r="HO2" s="3" t="inlineStr">
         <is>
           <t>SALLY</t>
         </is>
       </c>
-      <c r="HM2" s="3" t="inlineStr">
+      <c r="HP2" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="HN2"/>
-      <c r="HO2"/>
-      <c r="HP2"/>
       <c r="HQ2"/>
-      <c r="HR2" s="3" t="inlineStr">
+      <c r="HR2"/>
+      <c r="HS2"/>
+      <c r="HT2"/>
+      <c r="HU2" s="3" t="inlineStr">
         <is>
           <t>ORDPRV2468</t>
         </is>
       </c>
-      <c r="HS2" s="3" t="inlineStr">
+      <c r="HV2" s="3" t="inlineStr">
         <is>
           <t>SMITH</t>
         </is>
       </c>
-      <c r="HT2" s="3" t="inlineStr">
+      <c r="HW2" s="3" t="inlineStr">
         <is>
           <t>JOHN</t>
         </is>
       </c>
-      <c r="HU2" s="3" t="inlineStr">
+      <c r="HX2" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="HV2"/>
-      <c r="HW2"/>
-      <c r="HX2"/>
       <c r="HY2"/>
-      <c r="HZ2" s="3" t="inlineStr">
+      <c r="HZ2"/>
+      <c r="IA2"/>
+      <c r="IB2"/>
+      <c r="IC2" s="3" t="inlineStr">
         <is>
           <t>9995553336</t>
         </is>
       </c>
-      <c r="IA2" s="3" t="inlineStr">
+      <c r="ID2" s="3" t="inlineStr">
         <is>
           <t>DAVIDSON</t>
         </is>
       </c>
-      <c r="IB2" s="3" t="inlineStr">
+      <c r="IE2" s="3" t="inlineStr">
         <is>
           <t>MICHELLE</t>
         </is>
       </c>
-      <c r="IC2" s="3" t="inlineStr">
+      <c r="IF2" s="3" t="inlineStr">
         <is>
           <t>S</t>
         </is>
       </c>
-      <c r="ID2"/>
-      <c r="IE2"/>
-      <c r="IF2"/>
       <c r="IG2"/>
-      <c r="IH2" s="3" t="inlineStr">
+      <c r="IH2"/>
+      <c r="II2"/>
+      <c r="IJ2"/>
+      <c r="IK2" s="3" t="inlineStr">
         <is>
           <t>1689432123</t>
         </is>
       </c>
-      <c r="II2" s="3" t="inlineStr">
+      <c r="IL2" s="3" t="inlineStr">
         <is>
           <t>BEST HEALTH CENTER</t>
         </is>
       </c>
-      <c r="IJ2" s="3" t="inlineStr">
+      <c r="IM2" s="3" t="inlineStr">
         <is>
           <t>123 HEALTHY ST</t>
         </is>
       </c>
-      <c r="IK2" s="3" t="inlineStr">
+      <c r="IN2" s="3" t="inlineStr">
         <is>
           <t>SUITE 2000</t>
         </is>
       </c>
-      <c r="IL2" s="3" t="inlineStr">
+      <c r="IO2" s="3" t="inlineStr">
         <is>
           <t>FAIRFAX</t>
         </is>
       </c>
-      <c r="IM2" s="3" t="inlineStr">
+      <c r="IP2" s="3" t="inlineStr">
         <is>
           <t>VA</t>
         </is>
       </c>
-      <c r="IN2" s="3" t="inlineStr">
+      <c r="IQ2" s="3" t="inlineStr">
         <is>
           <t>22042</t>
         </is>
       </c>
-      <c r="IO2"/>
-      <c r="IP2"/>
-      <c r="IQ2"/>
       <c r="IR2"/>
-      <c r="IS2" s="3" t="inlineStr">
+      <c r="IS2"/>
+      <c r="IT2"/>
+      <c r="IU2"/>
+      <c r="IV2" s="3" t="inlineStr">
         <is>
           <t>PRIMARY</t>
         </is>
       </c>
-      <c r="IT2" s="3" t="inlineStr">
+      <c r="IW2" s="3" t="inlineStr">
         <is>
           <t>SELF</t>
         </is>
       </c>
-      <c r="IU2" s="3" t="inlineStr">
+      <c r="IX2" s="3" t="inlineStr">
         <is>
           <t>GR00786</t>
         </is>
       </c>
-      <c r="IV2" s="3" t="inlineStr">
+      <c r="IY2" s="3" t="inlineStr">
         <is>
           <t>Other Insured Group Name</t>
         </is>
       </c>
-      <c r="IW2" s="3" t="inlineStr">
+      <c r="IZ2" s="3" t="inlineStr">
         <is>
           <t>CI</t>
         </is>
       </c>
-      <c r="IX2" s="3" t="inlineStr">
+      <c r="JA2" s="3" t="inlineStr">
         <is>
           <t>MEMBER_ID</t>
         </is>
       </c>
-      <c r="IY2" s="3" t="inlineStr">
+      <c r="JB2" s="3" t="inlineStr">
         <is>
           <t>123456789</t>
         </is>
       </c>
-      <c r="IZ2"/>
-      <c r="JA2" s="3" t="inlineStr">
+      <c r="JC2"/>
+      <c r="JD2" s="3" t="inlineStr">
         <is>
           <t>DOE</t>
         </is>
       </c>
-      <c r="JB2" s="3" t="inlineStr">
+      <c r="JE2" s="3" t="inlineStr">
         <is>
           <t>JANE</t>
         </is>
       </c>
-      <c r="JC2" s="3" t="inlineStr">
+      <c r="JF2" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="JD2" s="3" t="inlineStr">
+      <c r="JG2" s="3" t="inlineStr">
         <is>
           <t>444 ORANGE STREET</t>
         </is>
       </c>
-      <c r="JE2" s="3" t="inlineStr">
+      <c r="JH2" s="3" t="inlineStr">
         <is>
           <t>APT 4B</t>
         </is>
       </c>
-      <c r="JF2" s="3" t="inlineStr">
+      <c r="JI2" s="3" t="inlineStr">
         <is>
           <t>LAKEVILLE</t>
         </is>
       </c>
-      <c r="JG2" s="3" t="inlineStr">
+      <c r="JJ2" s="3" t="inlineStr">
         <is>
           <t>TX</t>
         </is>
       </c>
-      <c r="JH2" s="3" t="inlineStr">
+      <c r="JK2" s="3" t="inlineStr">
         <is>
           <t>557143298</t>
         </is>
       </c>
-      <c r="JI2" s="3" t="inlineStr">
+      <c r="JL2" s="3" t="inlineStr">
         <is>
           <t>CORRECTION</t>
         </is>
       </c>
-      <c r="JJ2" s="3" t="inlineStr">
+      <c r="JM2" s="3" t="inlineStr">
         <is>
           <t>26</t>
         </is>
       </c>
-      <c r="JK2" s="1" t="n">
+      <c r="JN2" s="1" t="n">
         <v>55.0</v>
       </c>
-      <c r="JL2" t="n">
+      <c r="JO2" t="n">
         <v>1.0</v>
       </c>
-      <c r="JM2" s="3" t="inlineStr">
+      <c r="JP2" s="3" t="inlineStr">
         <is>
           <t>CORRECTION</t>
         </is>
       </c>
-      <c r="JN2" s="3" t="inlineStr">
+      <c r="JQ2" s="3" t="inlineStr">
         <is>
           <t>90</t>
         </is>
       </c>
-      <c r="JO2" s="1" t="n">
+      <c r="JR2" s="1" t="n">
         <v>65.55</v>
       </c>
-      <c r="JP2" t="n">
+      <c r="JS2" t="n">
         <v>1.0</v>
       </c>
-      <c r="JQ2" s="3" t="inlineStr">
+      <c r="JT2" s="3" t="inlineStr">
         <is>
           <t>CORRECTION</t>
         </is>
       </c>
-      <c r="JR2" s="3" t="inlineStr">
+      <c r="JU2" s="3" t="inlineStr">
         <is>
           <t>70</t>
         </is>
       </c>
-      <c r="JS2" s="1" t="n">
+      <c r="JV2" s="1" t="n">
         <v>73.03</v>
       </c>
-      <c r="JT2" t="n">
+      <c r="JW2" t="n">
         <v>2.0</v>
       </c>
-      <c r="JU2" s="1" t="n">
+      <c r="JX2" s="1" t="n">
         <v>8852.72</v>
       </c>
-      <c r="JV2" s="1" t="n">
+      <c r="JY2" s="1" t="n">
         <v>780.0</v>
       </c>
-      <c r="JW2" s="1" t="n">
+      <c r="JZ2" s="1" t="n">
         <v>60.0</v>
       </c>
-      <c r="JX2" s="3" t="inlineStr">
+      <c r="KA2" s="3" t="inlineStr">
         <is>
           <t>CLAIM014</t>
         </is>
       </c>
-      <c r="JY2" s="3" t="inlineStr">
+      <c r="KB2" s="3" t="inlineStr">
         <is>
           <t>PAYOR_ID</t>
         </is>
       </c>
-      <c r="JZ2" s="3" t="inlineStr">
+      <c r="KC2" s="3" t="inlineStr">
         <is>
           <t>12345</t>
         </is>
       </c>
-      <c r="KA2" s="3" t="inlineStr">
+      <c r="KD2" s="3" t="inlineStr">
         <is>
           <t>987654321</t>
         </is>
       </c>
-      <c r="KB2" s="3" t="inlineStr">
+      <c r="KE2" s="3" t="inlineStr">
         <is>
           <t>OTHER PAYER</t>
         </is>
       </c>
-      <c r="KC2" s="3" t="inlineStr">
+      <c r="KF2" s="3" t="inlineStr">
         <is>
           <t>PO BOX 7901</t>
         </is>
       </c>
-      <c r="KD2" s="3" t="inlineStr">
+      <c r="KG2" s="3" t="inlineStr">
         <is>
           <t>DEP 2</t>
         </is>
       </c>
-      <c r="KE2" s="3" t="inlineStr">
+      <c r="KH2" s="3" t="inlineStr">
         <is>
           <t>MADISON</t>
         </is>
       </c>
-      <c r="KF2" s="3" t="inlineStr">
+      <c r="KI2" s="3" t="inlineStr">
         <is>
           <t>MA</t>
         </is>
       </c>
-      <c r="KG2" s="3" t="inlineStr">
+      <c r="KJ2" s="3" t="inlineStr">
         <is>
           <t>53707</t>
         </is>
       </c>
-      <c r="KH2" s="3" t="inlineStr">
+      <c r="KK2" s="3" t="inlineStr">
         <is>
           <t>CLAIM_OFFICE_NUMBER</t>
         </is>
       </c>
-      <c r="KI2" s="3" t="inlineStr">
+      <c r="KL2" s="3" t="inlineStr">
         <is>
           <t>98765</t>
         </is>
       </c>
-      <c r="KJ2"/>
-      <c r="KK2"/>
-      <c r="KL2" s="3" t="inlineStr">
+      <c r="KM2"/>
+      <c r="KN2"/>
+      <c r="KO2" s="3" t="inlineStr">
         <is>
           <t>LX0004-1</t>
         </is>
       </c>
-      <c r="KM2" s="3" t="inlineStr">
+      <c r="KP2" s="3" t="inlineStr">
         <is>
           <t>0300</t>
         </is>
       </c>
-      <c r="KN2" s="3" t="inlineStr">
+      <c r="KQ2" s="3" t="inlineStr">
         <is>
           <t>81099</t>
         </is>
       </c>
-      <c r="KO2" s="3" t="inlineStr">
+      <c r="KR2" s="3" t="inlineStr">
         <is>
           <t>Short description</t>
         </is>
       </c>
-      <c r="KP2" s="3" t="inlineStr">
+      <c r="KS2" s="3" t="inlineStr">
         <is>
           <t>A1</t>
         </is>
       </c>
-      <c r="KQ2" s="3" t="inlineStr">
+      <c r="KT2" s="3" t="inlineStr">
         <is>
           <t>05</t>
         </is>
       </c>
-      <c r="KR2" s="3" t="inlineStr">
+      <c r="KU2" s="3" t="inlineStr">
         <is>
           <t>02</t>
         </is>
       </c>
-      <c r="KS2" s="3" t="inlineStr">
+      <c r="KV2" s="3" t="inlineStr">
         <is>
           <t>01</t>
         </is>
       </c>
-      <c r="KT2" s="1" t="n">
+      <c r="KW2" s="1" t="n">
         <v>173.42</v>
       </c>
-      <c r="KU2" s="3" t="inlineStr">
+      <c r="KX2" s="3" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="KV2" t="n">
+      <c r="KY2" t="n">
         <v>1.0</v>
       </c>
-      <c r="KW2" s="1" t="n">
+      <c r="KZ2" s="1" t="n">
         <v>11.07</v>
       </c>
-      <c r="KX2" s="4" t="n">
+      <c r="LA2" s="4" t="n">
         <v>43534.0</v>
       </c>
-      <c r="KY2" s="4" t="n">
+      <c r="LB2" s="4" t="n">
         <v>43596.0</v>
       </c>
-      <c r="KZ2" s="3" t="inlineStr">
+      <c r="LC2" s="3" t="inlineStr">
         <is>
           <t>Repriced</t>
         </is>
       </c>
-      <c r="LA2" s="3" t="inlineStr">
+      <c r="LD2" s="3" t="inlineStr">
         <is>
           <t>AdjRepriced</t>
         </is>
       </c>
-      <c r="LB2" s="1" t="n">
+      <c r="LE2" s="1" t="n">
         <v>15.0</v>
       </c>
-      <c r="LC2" s="1" t="n">
+      <c r="LF2" s="1" t="n">
         <v>22.0</v>
       </c>
-      <c r="LD2" s="3" t="inlineStr">
+      <c r="LG2" s="3" t="inlineStr">
         <is>
           <t>state regulation 123 was applied during the pricing of this claim</t>
         </is>
       </c>
-      <c r="LE2" s="3" t="inlineStr">
+      <c r="LH2" s="3" t="inlineStr">
         <is>
           <t>00002143481</t>
         </is>
       </c>
-      <c r="LF2" t="n">
+      <c r="LI2" t="n">
         <v>1.01</v>
       </c>
-      <c r="LG2" s="3" t="inlineStr">
+      <c r="LJ2" s="3" t="inlineStr">
         <is>
           <t>GRAM</t>
         </is>
       </c>
-      <c r="LH2" s="3" t="inlineStr">
+      <c r="LK2" s="3" t="inlineStr">
         <is>
           <t>123456</t>
         </is>
       </c>
-      <c r="LI2" s="3" t="inlineStr">
+      <c r="LL2" s="3" t="inlineStr">
         <is>
           <t>OZ</t>
         </is>
       </c>
-      <c r="LJ2" s="3" t="inlineStr">
+      <c r="LM2" s="3" t="inlineStr">
         <is>
           <t>FT</t>
         </is>
       </c>
-      <c r="LK2" s="3" t="inlineStr">
+      <c r="LN2" s="3" t="inlineStr">
         <is>
           <t>DMN0012</t>
         </is>
       </c>
-      <c r="LL2"/>
-      <c r="LM2"/>
-      <c r="LN2"/>
       <c r="LO2"/>
       <c r="LP2"/>
       <c r="LQ2"/>
-      <c r="LR2" s="3" t="inlineStr">
+      <c r="LR2"/>
+      <c r="LS2"/>
+      <c r="LT2"/>
+      <c r="LU2" s="3" t="inlineStr">
         <is>
           <t>OPRPHY4321</t>
         </is>
       </c>
-      <c r="LS2" s="3" t="inlineStr">
+      <c r="LV2" s="3" t="inlineStr">
         <is>
           <t>HAMILTON</t>
         </is>
       </c>
-      <c r="LT2" s="3" t="inlineStr">
+      <c r="LW2" s="3" t="inlineStr">
         <is>
           <t>ANAYA</t>
         </is>
       </c>
-      <c r="LU2" s="3" t="inlineStr">
+      <c r="LX2" s="3" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="LV2"/>
-      <c r="LW2"/>
-      <c r="LX2"/>
       <c r="LY2"/>
-      <c r="LZ2" s="3" t="inlineStr">
+      <c r="LZ2"/>
+      <c r="MA2"/>
+      <c r="MB2"/>
+      <c r="MC2" s="3" t="inlineStr">
         <is>
           <t>OTHOPR4321</t>
         </is>
       </c>
-      <c r="MA2" s="3" t="inlineStr">
+      <c r="MD2" s="3" t="inlineStr">
         <is>
           <t>BLUE</t>
         </is>
       </c>
-      <c r="MB2" s="3" t="inlineStr">
+      <c r="ME2" s="3" t="inlineStr">
         <is>
           <t>KELLY</t>
         </is>
       </c>
-      <c r="MC2" s="3" t="inlineStr">
+      <c r="MF2" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="MD2"/>
-      <c r="ME2"/>
-      <c r="MF2"/>
       <c r="MG2"/>
-      <c r="MH2" s="3" t="inlineStr">
+      <c r="MH2"/>
+      <c r="MI2"/>
+      <c r="MJ2"/>
+      <c r="MK2" s="3" t="inlineStr">
         <is>
           <t>9998887777</t>
         </is>
       </c>
-      <c r="MI2" s="3" t="inlineStr">
+      <c r="ML2" s="3" t="inlineStr">
         <is>
           <t>BIG</t>
         </is>
       </c>
-      <c r="MJ2" s="3" t="inlineStr">
+      <c r="MM2" s="3" t="inlineStr">
         <is>
           <t>ANNA</t>
         </is>
       </c>
-      <c r="MK2" s="3" t="inlineStr">
+      <c r="MN2" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="ML2"/>
-      <c r="MM2"/>
-      <c r="MN2"/>
       <c r="MO2"/>
-      <c r="MP2" s="3" t="inlineStr">
+      <c r="MP2"/>
+      <c r="MQ2"/>
+      <c r="MR2"/>
+      <c r="MS2" s="3" t="inlineStr">
         <is>
           <t>REFPRV8642</t>
         </is>
       </c>
-      <c r="MQ2" s="3" t="inlineStr">
+      <c r="MT2" s="3" t="inlineStr">
         <is>
           <t>THRONBERRY</t>
         </is>
       </c>
-      <c r="MR2" s="3" t="inlineStr">
+      <c r="MU2" s="3" t="inlineStr">
         <is>
           <t>JOHN</t>
         </is>
       </c>
-      <c r="MS2" s="3" t="inlineStr">
+      <c r="MV2" s="3" t="inlineStr">
         <is>
           <t>L</t>
         </is>
       </c>
-      <c r="MT2"/>
-      <c r="MU2"/>
-      <c r="MV2"/>
       <c r="MW2"/>
+      <c r="MX2"/>
+      <c r="MY2"/>
+      <c r="MZ2"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>6a32cb6497613a0e49909442</t>
+          <t>6aaaca96b439338235b48e7d</t>
         </is>
       </c>
       <c r="B3"/>
@@ -3534,206 +3560,209 @@
       <c r="KI3"/>
       <c r="KJ3"/>
       <c r="KK3"/>
-      <c r="KL3" s="3" t="inlineStr">
+      <c r="KL3"/>
+      <c r="KM3"/>
+      <c r="KN3"/>
+      <c r="KO3" s="3" t="inlineStr">
         <is>
           <t>LX0004-2</t>
         </is>
       </c>
-      <c r="KM3" s="3" t="inlineStr">
+      <c r="KP3" s="3" t="inlineStr">
         <is>
           <t>0730</t>
         </is>
       </c>
-      <c r="KN3" s="3" t="inlineStr">
+      <c r="KQ3" s="3" t="inlineStr">
         <is>
           <t>00842</t>
         </is>
       </c>
-      <c r="KO3" s="3" t="inlineStr">
+      <c r="KR3" s="3" t="inlineStr">
         <is>
           <t>Sample procedure</t>
         </is>
       </c>
-      <c r="KP3" s="3" t="inlineStr">
+      <c r="KS3" s="3" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="KQ3" s="3" t="inlineStr">
+      <c r="KT3" s="3" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="KR3" s="3" t="inlineStr">
+      <c r="KU3" s="3" t="inlineStr">
         <is>
           <t>34</t>
         </is>
       </c>
-      <c r="KS3" s="3" t="inlineStr">
+      <c r="KV3" s="3" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="KT3" s="1" t="n">
+      <c r="KW3" s="1" t="n">
         <v>86.54</v>
       </c>
-      <c r="KU3" s="3" t="inlineStr">
+      <c r="KX3" s="3" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="KV3" t="n">
+      <c r="KY3" t="n">
         <v>1.0</v>
       </c>
-      <c r="KW3" s="1" t="n">
+      <c r="KZ3" s="1" t="n">
         <v>28.01</v>
       </c>
-      <c r="KX3" s="4" t="n">
+      <c r="LA3" s="4" t="n">
         <v>43534.0</v>
       </c>
-      <c r="KY3" s="4" t="n">
+      <c r="LB3" s="4" t="n">
         <v>43534.0</v>
       </c>
-      <c r="KZ3"/>
-      <c r="LA3"/>
-      <c r="LB3"/>
       <c r="LC3"/>
       <c r="LD3"/>
-      <c r="LE3" s="3" t="inlineStr">
+      <c r="LE3"/>
+      <c r="LF3"/>
+      <c r="LG3"/>
+      <c r="LH3" s="3" t="inlineStr">
         <is>
           <t>00093-0051-05</t>
         </is>
       </c>
-      <c r="LF3" t="n">
+      <c r="LI3" t="n">
         <v>5.0</v>
       </c>
-      <c r="LG3" s="3" t="inlineStr">
+      <c r="LJ3" s="3" t="inlineStr">
         <is>
           <t>UNIT</t>
         </is>
       </c>
-      <c r="LH3" s="3" t="inlineStr">
+      <c r="LK3" s="3" t="inlineStr">
         <is>
           <t>945632</t>
         </is>
       </c>
-      <c r="LI3" s="3" t="inlineStr">
+      <c r="LL3" s="3" t="inlineStr">
         <is>
           <t>08</t>
         </is>
       </c>
-      <c r="LJ3" s="3" t="inlineStr">
+      <c r="LM3" s="3" t="inlineStr">
         <is>
           <t>EL</t>
         </is>
       </c>
-      <c r="LK3" s="3" t="inlineStr">
+      <c r="LN3" s="3" t="inlineStr">
         <is>
           <t>TPM0048</t>
         </is>
       </c>
-      <c r="LL3"/>
-      <c r="LM3"/>
-      <c r="LN3"/>
       <c r="LO3"/>
       <c r="LP3"/>
       <c r="LQ3"/>
-      <c r="LR3" s="3" t="inlineStr">
+      <c r="LR3"/>
+      <c r="LS3"/>
+      <c r="LT3"/>
+      <c r="LU3" s="3" t="inlineStr">
         <is>
           <t>OPRPHY4321</t>
         </is>
       </c>
-      <c r="LS3" s="3" t="inlineStr">
+      <c r="LV3" s="3" t="inlineStr">
         <is>
           <t>HAMILTON</t>
         </is>
       </c>
-      <c r="LT3" s="3" t="inlineStr">
+      <c r="LW3" s="3" t="inlineStr">
         <is>
           <t>ANAYA</t>
         </is>
       </c>
-      <c r="LU3" s="3" t="inlineStr">
+      <c r="LX3" s="3" t="inlineStr">
         <is>
           <t>H</t>
         </is>
       </c>
-      <c r="LV3"/>
-      <c r="LW3"/>
-      <c r="LX3"/>
       <c r="LY3"/>
-      <c r="LZ3" s="3" t="inlineStr">
+      <c r="LZ3"/>
+      <c r="MA3"/>
+      <c r="MB3"/>
+      <c r="MC3" s="3" t="inlineStr">
         <is>
           <t>OTHOPR4321</t>
         </is>
       </c>
-      <c r="MA3" s="3" t="inlineStr">
+      <c r="MD3" s="3" t="inlineStr">
         <is>
           <t>BLUE</t>
         </is>
       </c>
-      <c r="MB3" s="3" t="inlineStr">
+      <c r="ME3" s="3" t="inlineStr">
         <is>
           <t>KELLY</t>
         </is>
       </c>
-      <c r="MC3" s="3" t="inlineStr">
+      <c r="MF3" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="MD3"/>
-      <c r="ME3"/>
-      <c r="MF3"/>
       <c r="MG3"/>
-      <c r="MH3" s="3" t="inlineStr">
+      <c r="MH3"/>
+      <c r="MI3"/>
+      <c r="MJ3"/>
+      <c r="MK3" s="3" t="inlineStr">
         <is>
           <t>9998887777</t>
         </is>
       </c>
-      <c r="MI3" s="3" t="inlineStr">
+      <c r="ML3" s="3" t="inlineStr">
         <is>
           <t>BIG</t>
         </is>
       </c>
-      <c r="MJ3" s="3" t="inlineStr">
+      <c r="MM3" s="3" t="inlineStr">
         <is>
           <t>ANNA</t>
         </is>
       </c>
-      <c r="MK3" s="3" t="inlineStr">
+      <c r="MN3" s="3" t="inlineStr">
         <is>
           <t>A</t>
         </is>
       </c>
-      <c r="ML3"/>
-      <c r="MM3"/>
-      <c r="MN3"/>
       <c r="MO3"/>
-      <c r="MP3" s="3" t="inlineStr">
+      <c r="MP3"/>
+      <c r="MQ3"/>
+      <c r="MR3"/>
+      <c r="MS3" s="3" t="inlineStr">
         <is>
           <t>REFPRV8642</t>
         </is>
       </c>
-      <c r="MQ3" s="3" t="inlineStr">
+      <c r="MT3" s="3" t="inlineStr">
         <is>
           <t>THRONBERRY</t>
         </is>
       </c>
-      <c r="MR3" s="3" t="inlineStr">
+      <c r="MU3" s="3" t="inlineStr">
         <is>
           <t>JOHN</t>
         </is>
       </c>
-      <c r="MS3" s="3" t="inlineStr">
+      <c r="MV3" s="3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="MT3"/>
-      <c r="MU3"/>
-      <c r="MV3"/>
       <c r="MW3"/>
+      <c r="MX3"/>
+      <c r="MY3"/>
+      <c r="MZ3"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
